--- a/1_Data/Vicovaro_2024_PeerJ/Exp2/Codebook_Vicovaro_2024_PeerJ_Exp2_Clean.xlsx
+++ b/1_Data/Vicovaro_2024_PeerJ/Exp2/Codebook_Vicovaro_2024_PeerJ_Exp2_Clean.xlsx
@@ -1,159 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
-  <si>
-    <t xml:space="preserve">Variable_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable_category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Participant number (1-64)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numerical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trial number within the matching task (1-240, data row order; block 1 trials 1-120, block 2 trials 121-240)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block number (1-2; 120 trials per block)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual geometric shape presented (circle or square; the author export only recorded the identity, so the shape is recovered per subject from the author OrdineP#.xlsx files for subjects 1-40 and extrapolated by the 4-circle/4-square alternation for subjects 41-64 - see the study JSON detail; original identity kept in raw ShapeIdentity and in Shape_Origin_Identity)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">circle;square</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Categorical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label identity paired with the shape on that trial, derived: Matching trials pair the shape with its own label, Nonmatching trials with the opposite label</t>
-  </si>
-  <si>
-    <t xml:space="preserve">you;stranger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whether the shape-label pair matches the learned association (Matching/Nonmatching)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matching;Nonmatching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accuracy: 1 = correct; 0 = incorrect; NA = no response (missed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA;0;1;NA (no response)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RT_ms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reaction time in milliseconds (author export values; may contain negative values = early keypresses and values beyond the 1000 ms response window, kept as-is per minimal preprocessing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label_Origin_Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original label identity (you/stranger)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label_English_Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English form of the label identity (You/Stranger)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You;Stranger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Label_Standardized_Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standardized identity (Self/Stranger)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Self;Stranger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shape_Origin_Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original identity of the presented shape (you/stranger)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shape_English_Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English form of the shape identity (You/Stranger)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shape_Standardized_Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standardized identity of the shape (Self/Stranger)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -172,12 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -227,6 +170,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -252,12 +199,15 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -283,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -459,222 +408,367 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Variable_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Variable_description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Variable_value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Variable_category</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Participant number (1-64)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Block number (1-2; 120 trials per block)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Trial number within the matching task (1-240, data row order; block 1 trials 1-120, block 2 trials 121-240)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shape</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Actual geometric shape presented (circle or square; the author export only recorded the identity, so the shape is recovered per subject from the author OrdineP#.xlsx files for subjects 1-40 and extrapolated by the 4-circle/4-square alternation for subjects 41-64 - see the study JSON detail; original identity kept in raw ShapeIdentity and in Shape_Origin_Identity)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>circle;square</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Label identity paired with the shape on that trial, derived: Matching trials pair the shape with its own label, Nonmatching trials with the opposite label</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>you;stranger</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>self-matching</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Matching</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Whether the shape-label pair matches the learned association (Matching/Nonmatching)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Matching;Nonmatching</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Label_Origin_Identity</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Original label identity (you/stranger)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>you;stranger</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Label_English_Identity</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>English form of the label identity (You/Stranger)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>You;Stranger</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>15</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Label_Standardized_Identity</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Standardized identity (Self/Stranger)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Self;Stranger</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>15</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shape_Origin_Identity</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Original identity of the presented shape (you/stranger)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>you;stranger</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Shape_English_Identity</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>English form of the shape identity (You/Stranger)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>You;Stranger</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Shape_Standardized_Identity</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Standardized identity of the shape (Self/Stranger)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Self;Stranger</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" t="s">
-        <v>15</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RT_ms</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Reaction time in milliseconds (author export values; may contain negative values = early keypresses and values beyond the 1000 ms response window, kept as-is per minimal preprocessing)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Accuracy: 1 = correct; 0 = incorrect; NA = no response (missed)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NA;0;1;NA (no response)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>